--- a/laporan_padel_dki_jakarta_2026-09-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-19.xlsx
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.593.000</t>
+          <t>Rp2.718.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>56</v>
       </c>
       <c r="D49" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.898.000</t>
+          <t>Rp2.448.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.780.000</t>
+          <t>Rp2.855.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>96</v>
       </c>
       <c r="D77" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp11.940.000</t>
+          <t>Rp12.340.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp9.610.000</t>
+          <t>Rp10.195.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp11.800.000</t>
+          <t>Rp13.050.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5211,14 +5211,14 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.373.000</t>
+          <t>Rp1.446.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5586,21 +5586,21 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -5699,16 +5699,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.990.000</t>
+          <t>Rp13.290.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp19.450.000</t>
+          <t>Rp21.575.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp894.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.289.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.170.000</t>
+          <t>Rp2.320.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.834.000</t>
+          <t>Rp13.104.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.740.000</t>
+          <t>Rp1.885.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp13.230.000</t>
+          <t>Rp12.390.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.960.000</t>
+          <t>Rp3.330.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-19.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.660.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.936.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.815.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp19.876.500</t>
+          <t>Rp20.289.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp17.810.000</t>
+          <t>Rp18.060.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp31.294.000</t>
+          <t>Rp31.992.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.626.000</t>
+          <t>Rp4.026.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.072.000</t>
+          <t>Rp4.664.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.086.000</t>
+          <t>Rp6.444.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>51</v>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.465.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp775.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.730.000</t>
+          <t>Rp1.930.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>56</v>
       </c>
       <c r="D49" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.448.000</t>
+          <t>Rp1.898.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.048.000</t>
+          <t>Rp6.624.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp894.000</t>
+          <t>Rp1.341.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.990.000</t>
+          <t>Rp6.710.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.855.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>112</v>
       </c>
       <c r="D74" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp5.870.000</t>
+          <t>Rp4.110.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>96</v>
       </c>
       <c r="D77" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>34</v>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>68</v>
       </c>
       <c r="D95" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.268.000</t>
+          <t>Rp2.349.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp20.228.000</t>
+          <t>Rp24.896.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.190.000</t>
+          <t>Rp3.510.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp12.250.000</t>
+          <t>Rp13.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp10.195.000</t>
+          <t>Rp10.985.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.396.000</t>
+          <t>Rp2.396.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp13.050.000</t>
+          <t>Rp14.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.545.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.980.000</t>
+          <t>Rp6.578.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp19.350.000</t>
+          <t>Rp19.500.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>68</v>
       </c>
       <c r="D43" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D52" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp8.450.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp8.195.000</t>
+          <t>Rp8.855.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.446.000</t>
+          <t>Rp2.258.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.310.000</t>
+          <t>Rp5.490.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.545.000</t>
+          <t>Rp6.930.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp16.200.000</t>
+          <t>Rp16.700.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.320.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp23.700.000</t>
+          <t>Rp25.300.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.480.000</t>
+          <t>Rp3.160.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.190.000</t>
+          <t>Rp6.890.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp752.000</t>
+          <t>Rp1.316.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.290.000</t>
+          <t>Rp13.470.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp17.410.000</t>
+          <t>Rp17.800.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp20.150.000</t>
+          <t>Rp20.975.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp21.040.000</t>
+          <t>Rp21.590.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.750.000</t>
+          <t>Rp12.300.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp6.175.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.695.000</t>
+          <t>Rp7.776.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.256.000</t>
+          <t>Rp2.444.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp22.454.000</t>
+          <t>Rp23.650.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>174</v>
       </c>
       <c r="D43" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp32.500.000</t>
+          <t>Rp30.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>108</v>
       </c>
       <c r="D46" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp9.100.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.760.000</t>
+          <t>Rp4.380.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7878,16 +7878,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.859.000</t>
+          <t>Rp2.197.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.505.000</t>
+          <t>Rp7.555.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.150.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp8.330.000</t>
+          <t>Rp7.990.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp13.104.000</t>
+          <t>Rp12.504.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.885.000</t>
+          <t>Rp2.320.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp12.390.000</t>
+          <t>Rp13.230.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.345.000</t>
+          <t>Rp5.580.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.860.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.704.000</t>
+          <t>Rp3.042.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-19.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp11.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.138.000</t>
+          <t>Rp6.435.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.285.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp20.289.000</t>
+          <t>Rp21.251.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.880.000</t>
+          <t>Rp8.040.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.992.000</t>
+          <t>Rp2.241.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp31.992.000</t>
+          <t>Rp32.790.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp298.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.026.000</t>
+          <t>Rp4.296.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp4.640.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.280.000</t>
+          <t>Rp4.150.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.444.000</t>
+          <t>Rp6.981.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.718.000</t>
+          <t>Rp3.108.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp775.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>56</v>
       </c>
       <c r="D49" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.898.000</t>
+          <t>Rp2.998.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.624.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.341.000</t>
+          <t>Rp1.490.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>153</v>
       </c>
       <c r="D59" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.639.000</t>
+          <t>Rp1.490.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp3.657.000</t>
+          <t>Rp3.757.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>72</v>
       </c>
       <c r="D61" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.208.000</t>
+          <t>Rp2.828.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp4.888.000</t>
+          <t>Rp6.084.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>128</v>
       </c>
       <c r="D68" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.189.000</t>
+          <t>Rp3.383.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp6.710.000</t>
+          <t>Rp6.560.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.110.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>54</v>
       </c>
       <c r="D79" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp2.115.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp1.193.000</t>
+          <t>Rp1.318.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.339.013</t>
+          <t>Rp19.624.013</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp24.896.000</t>
+          <t>Rp26.452.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>54</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp3.990.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.396.000</t>
+          <t>Rp2.596.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp14.450.000</t>
+          <t>Rp14.800.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.645.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.455.000</t>
+          <t>Rp1.955.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp19.500.000</t>
+          <t>Rp17.250.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>68</v>
       </c>
       <c r="D43" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D52" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp8.675.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp8.855.000</t>
+          <t>Rp9.680.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5211,14 +5211,14 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D58" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.258.000</t>
+          <t>Rp2.623.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.320.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp12.300.000</t>
+          <t>Rp12.600.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.490.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.930.000</t>
+          <t>Rp9.047.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp25.300.000</t>
+          <t>Rp22.100.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp3.910.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.482.000</t>
+          <t>Rp3.978.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.890.000</t>
+          <t>Rp7.940.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.316.000</t>
+          <t>Rp1.504.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.470.000</t>
+          <t>Rp13.890.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.370.000</t>
+          <t>Rp11.930.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.029.000</t>
+          <t>Rp1.129.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp17.800.000</t>
+          <t>Rp18.190.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp20.975.000</t>
+          <t>Rp22.075.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp11.802.000</t>
+          <t>Rp12.302.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.776.000</t>
+          <t>Rp7.857.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.444.000</t>
+          <t>Rp2.632.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp894.000</t>
+          <t>Rp1.192.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.775.000</t>
+          <t>Rp7.425.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7486,21 +7486,21 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp23.650.000</t>
+          <t>Rp25.596.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp300.000</t>
+          <t>Rp200.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -7548,16 +7548,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp11.750.000</t>
+          <t>Rp11.925.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>108</v>
       </c>
       <c r="D46" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp9.100.000</t>
+          <t>Rp11.700.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.380.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>48</v>
       </c>
       <c r="D49" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.870.000</t>
+          <t>Rp16.720.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.555.000</t>
+          <t>Rp8.655.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.320.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.990.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.504.000</t>
+          <t>Rp12.954.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.320.000</t>
+          <t>Rp2.755.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.470.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.855.000</t>
+          <t>Rp4.005.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp825.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp13.230.000</t>
+          <t>Rp13.860.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.625.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.580.000</t>
+          <t>Rp5.855.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.535.000</t>
+          <t>Rp6.345.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-19.xlsx
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.530.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.075.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp3.757.000</t>
+          <t>Rp3.916.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>72</v>
       </c>
       <c r="D61" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.828.000</t>
+          <t>Rp3.208.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.130.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>85</v>
       </c>
       <c r="D78" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>64</v>
       </c>
       <c r="D93" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.190.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp12.340.000</t>
+          <t>Rp12.460.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp26.452.000</t>
+          <t>Rp27.230.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.990.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>180</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp31.845.000</t>
+          <t>Rp32.395.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp7.125.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D52" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.675.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.623.000</t>
+          <t>Rp2.867.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp12.600.000</t>
+          <t>Rp13.200.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.491.000</t>
+          <t>Rp1.788.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.890.000</t>
+          <t>Rp13.480.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.129.000</t>
+          <t>Rp1.198.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>108</v>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.136.000</t>
+          <t>Rp5.264.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp12.302.000</t>
+          <t>Rp12.478.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp32.900.000</t>
+          <t>Rp33.100.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.169.000</t>
+          <t>Rp6.368.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.460.000</t>
+          <t>Rp8.060.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.192.000</t>
+          <t>Rp1.341.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp25.596.000</t>
+          <t>Rp27.142.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp11.925.000</t>
+          <t>Rp12.275.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>102</v>
       </c>
       <c r="D44" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>108</v>
       </c>
       <c r="D46" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp11.700.000</t>
+          <t>Rp12.350.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.020.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>48</v>
       </c>
       <c r="D49" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7878,16 +7878,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.197.000</t>
+          <t>Rp2.535.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.720.000</t>
+          <t>Rp16.910.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.755.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.005.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.345.000</t>
+          <t>Rp6.480.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.042.000</t>
+          <t>Rp4.056.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-19.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-19.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.870.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.000.000</t>
+          <t>Rp11.300.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.288.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.285.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp21.251.500</t>
+          <t>Rp21.329.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.040.000</t>
+          <t>Rp8.520.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp18.060.000</t>
+          <t>Rp18.670.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.425.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.664.000</t>
+          <t>Rp4.812.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.981.000</t>
+          <t>Rp7.160.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.108.000</t>
+          <t>Rp3.303.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>96</v>
       </c>
       <c r="D46" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp7.905.000</t>
+          <t>Rp8.232.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp135.000</t>
+          <t>Rp260.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.490.000</t>
+          <t>Rp1.639.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp347.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>32</v>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp6.560.000</t>
+          <t>Rp6.760.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>85</v>
       </c>
       <c r="D78" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>36</v>
       </c>
       <c r="D80" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>32</v>
       </c>
       <c r="D96" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.349.000</t>
+          <t>Rp2.673.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.624.013</t>
+          <t>Rp19.975.013</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.955.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp9.075.000</t>
+          <t>Rp9.275.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp17.250.000</t>
+          <t>Rp17.550.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>131</v>
       </c>
       <c r="D58" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp10.450.000</t>
+          <t>Rp9.850.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.788.000</t>
+          <t>Rp1.689.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.480.000</t>
+          <t>Rp13.880.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.198.000</t>
+          <t>Rp1.872.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp12.478.000</t>
+          <t>Rp12.654.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.857.000</t>
+          <t>Rp8.181.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp2.730.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.632.000</t>
+          <t>Rp3.008.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.330.000</t>
+          <t>Rp3.515.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.480.000</t>
+          <t>Rp6.885.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
